--- a/resampling/input/accessibility_reports_generated/Street Child of Nigeria_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_generated/Street Child of Nigeria_accessibility_report.xlsx
@@ -184,8 +184,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q27" headerRowCount="1">
-  <autoFilter ref="A1:Q27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WardAccessibility" displayName="WardAccessibility" ref="A1:Q39" headerRowCount="1">
+  <autoFilter ref="A1:Q39"/>
   <tableColumns count="17">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -210,8 +210,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O59" headerRowCount="1">
-  <autoFilter ref="A1:O59"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O45" headerRowCount="1">
+  <autoFilter ref="A1:O45"/>
   <tableColumns count="15">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
@@ -553,7 +553,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Assigned to you: 26 wards, 58 clusters</t>
+          <t>Assigned to you: 38 wards, 44 clusters</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -849,13 +849,13 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
+        <v>11</v>
+      </c>
+      <c r="I2" t="n">
         <v>5</v>
       </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
       <c r="J2" t="n">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -894,13 +894,13 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -923,29 +923,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sukur</t>
+          <t>Garta</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sukur</t>
+          <t>Pallam</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -968,14 +976,10 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pallam</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Pallam</t>
-        </is>
-      </c>
+          <t>Bebel</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>No</t>
@@ -984,13 +988,13 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1013,14 +1017,10 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Waga-Chakawa</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Waga-chakawa</t>
-        </is>
-      </c>
+          <t>Bita Izge</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>No</t>
@@ -1029,13 +1029,13 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1058,29 +1058,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hyambula</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Hyambula</t>
-        </is>
-      </c>
+          <t>Duhu</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1103,14 +1107,10 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Duhu</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Duhu</t>
-        </is>
-      </c>
+          <t>Hambagda Limankara Jaje</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>No</t>
@@ -1119,13 +1119,13 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -1148,14 +1148,10 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bita Izge</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Gulak</t>
-        </is>
-      </c>
+          <t>Hyambula</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>No</t>
@@ -1164,13 +1160,13 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -1193,29 +1189,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bebel</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Bebel</t>
-        </is>
-      </c>
+          <t>Kirchinga</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1238,29 +1238,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kirchinga</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Kirchinga</t>
-        </is>
-      </c>
+          <t>Ngurthavu Kopa</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1273,39 +1277,43 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Borno</t>
+          <t>Adamawa</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Madagali</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dikwa</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Boboshe</t>
-        </is>
-      </c>
+          <t>Ninkisi / Wuro Ngiki</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1318,24 +1326,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Borno</t>
+          <t>Adamawa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Madagali</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Gawa</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Boboshe</t>
-        </is>
-      </c>
+          <t>Pallam</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1343,7 +1347,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mafa</t>
+          <t>Michika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1352,13 +1356,13 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1371,24 +1375,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Borno</t>
+          <t>Adamawa</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Madagali</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mudu Kaza</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>M. Kaza</t>
-        </is>
-      </c>
+          <t>Sukur</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>No</t>
@@ -1397,13 +1397,13 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -1416,39 +1416,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Borno</t>
+          <t>Adamawa</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Madagali</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Gajibo</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Gajibo</t>
-        </is>
-      </c>
+          <t>Tumbara / Ngabili</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -1461,24 +1465,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Borno</t>
+          <t>Adamawa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Madagali</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Afuye</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Afuye</t>
-        </is>
-      </c>
+          <t>Waga-Chakawa</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>No</t>
@@ -1487,13 +1487,13 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -1506,24 +1506,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Borno</t>
+          <t>Adamawa</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Madagali</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Muliye</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Muliye</t>
-        </is>
-      </c>
+          <t>Wula</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>No</t>
@@ -1532,13 +1528,13 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -1556,34 +1552,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boboshe</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Boboshe</t>
+          <t>Kumalia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Guzamala; Kukawa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -1601,17 +1605,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Abbaram</t>
+          <t>Kekeno</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Muliye</t>
+          <t>Ngurno</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1621,7 +1625,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bama</t>
+          <t>Kukawa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1630,13 +1634,13 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1654,34 +1658,42 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mala Maja</t>
+          <t>Ngurno</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>M. Maja</t>
+          <t>Ngurno</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kukawa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -1704,12 +1716,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Monguno</t>
+          <t>Kumalia</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Kumalia</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1728,13 +1740,13 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>162</v>
+        <v>11</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1757,12 +1769,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wulo</t>
+          <t>Mandala</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wulo</t>
+          <t>Mandala</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1773,13 +1785,13 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -1802,29 +1814,37 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mintar</t>
+          <t>Sugundure</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mintar</t>
+          <t>Zulum</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Nganzai</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -1847,29 +1867,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kekeno</t>
+          <t>Yele</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ngurno</t>
+          <t>Yele</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Kukawa</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>1</v>
       </c>
@@ -1900,29 +1912,37 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mofio</t>
+          <t>Yoyo</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Damakuli</t>
+          <t>Kumalia</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Guzamala; Kukawa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
         <v>2</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>5</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -1945,29 +1965,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sure</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Sure</t>
-        </is>
-      </c>
+          <t>Alarge</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Guzamala; Nganzai</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
@@ -1990,14 +2014,10 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kaguram</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Mintar</t>
-        </is>
-      </c>
+          <t>Badairi</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>No</t>
@@ -2006,13 +2026,13 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
@@ -2022,23 +2042,579 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Damakulli</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mafa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" s="10" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Kabulawa</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mafa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" s="10" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Kaguram</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" s="10" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Kingarwa</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Guzamala</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" s="10" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Kirenowa</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" s="10" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Maiwa</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mafa; Nganzai</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" s="10" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Masu</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Jere; Mafa; Nganzai</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" s="10" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Mintar</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Kukawa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" s="10" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Mofio</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mafa; Nganzai</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" s="10" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Sure</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" s="10" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Wulo</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Guzamala</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" s="10" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Borno</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Monguno</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Zulum</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" s="10" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="K2:K27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2:L39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="O2:O39" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-08-28</formula2>
+      <formula2>2026-09-20</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2054,7 +2630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O59"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2213,7 +2789,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pallam</t>
+          <t>Madagali</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2223,7 +2799,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>idp_NG002010_10</t>
+          <t>idp_NG002010_15</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2262,7 +2838,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sukur</t>
+          <t>Madagali</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2272,7 +2848,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>idp_NG002010_11</t>
+          <t>idp_NG002010_16</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2311,7 +2887,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Waga-Chakawa</t>
+          <t>Madagali</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2321,7 +2897,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>idp_NG002010_12</t>
+          <t>idp_NG002010_17</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2360,7 +2936,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sukur</t>
+          <t>Gulak</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2370,7 +2946,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>idp_NG002010_13</t>
+          <t>idp_NG002010_6</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2380,12 +2956,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -2409,7 +2985,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Madagali</t>
+          <t>Gulak</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2419,7 +2995,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>idp_NG002010_15</t>
+          <t>idp_NG002010_supp1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2429,12 +3005,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -2458,7 +3034,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Madagali</t>
+          <t>Gulak</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2468,7 +3044,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>idp_NG002010_16</t>
+          <t>idp_NG002010_supp2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2507,7 +3083,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Madagali</t>
+          <t>Gulak</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2517,7 +3093,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>idp_NG002010_17</t>
+          <t>idp_NG002010_supp3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2556,7 +3132,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gulak</t>
+          <t>Madagali</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2566,7 +3142,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>idp_NG002010_6</t>
+          <t>idp_NG002010_supp4</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2605,7 +3181,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pallam</t>
+          <t>Madagali</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2615,7 +3191,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>idp_NG002010_7</t>
+          <t>idp_NG002010_supp5</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2625,12 +3201,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -2654,24 +3230,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hyambula</t>
+          <t>Gulak</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>idp_NG002010_9</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>In-host</t>
-        </is>
-      </c>
+          <t>non_idp_NG002010_1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>6</t>
@@ -2703,7 +3275,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Gulak</t>
+          <t>Madagali</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2713,18 +3285,18 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_1</t>
+          <t>non_idp_NG002010_15</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2748,7 +3320,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hyambula</t>
+          <t>Gulak</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2758,7 +3330,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_10</t>
+          <t>non_idp_NG002010_3</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -2793,7 +3365,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Waga-Chakawa</t>
+          <t>Gulak</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2803,18 +3375,18 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_11</t>
+          <t>non_idp_NG002010_4</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2838,7 +3410,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sukur</t>
+          <t>Gulak</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2848,7 +3420,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_12</t>
+          <t>non_idp_NG002010_7</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -2883,7 +3455,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bebel</t>
+          <t>Gulak</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2893,7 +3465,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_13</t>
+          <t>non_idp_NG002010_supp1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -2928,7 +3500,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bita Izge</t>
+          <t>Madagali</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2938,7 +3510,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_14</t>
+          <t>non_idp_NG002010_supp10</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -2973,7 +3545,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Madagali</t>
+          <t>Gulak</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2983,18 +3555,18 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_15</t>
+          <t>non_idp_NG002010_supp11</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3018,7 +3590,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Waga-Chakawa</t>
+          <t>Gulak</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3028,7 +3600,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_17</t>
+          <t>non_idp_NG002010_supp12</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -3063,7 +3635,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Duhu</t>
+          <t>Gulak</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3073,7 +3645,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_2</t>
+          <t>non_idp_NG002010_supp13</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -3118,7 +3690,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_3</t>
+          <t>non_idp_NG002010_supp2</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -3153,7 +3725,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Gulak</t>
+          <t>Garta</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3163,18 +3735,18 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_4</t>
+          <t>non_idp_NG002010_supp3</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3198,7 +3770,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Duhu</t>
+          <t>Gulak</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3208,7 +3780,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_6</t>
+          <t>non_idp_NG002010_supp4</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -3243,7 +3815,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Gulak</t>
+          <t>Madagali</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3253,7 +3825,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_7</t>
+          <t>non_idp_NG002010_supp8</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -3288,7 +3860,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hyambula</t>
+          <t>Gulak</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3298,7 +3870,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_8</t>
+          <t>non_idp_NG002010_supp9</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -3323,38 +3895,42 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Adamawa</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Madagali</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pallam</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_9</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>idp_NG008024_1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>In-camp</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3373,12 +3949,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3388,7 +3964,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>idp_NG008008_1</t>
+          <t>idp_NG008024_10</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3398,12 +3974,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3422,12 +3998,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3437,7 +4013,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>idp_NG008008_13</t>
+          <t>idp_NG008024_5</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3471,37 +4047,33 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>idp_NG008008_6</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>In-camp</t>
-        </is>
-      </c>
+          <t>non_idp_NG008024_11</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3520,12 +4092,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boboshe</t>
+          <t>Kekeno</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3535,7 +4107,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>non_idp_NG008008_1</t>
+          <t>non_idp_NG008024_2</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -3565,12 +4137,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3580,18 +4152,18 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>non_idp_NG008008_10</t>
+          <t>non_idp_NG008024_7</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3610,12 +4182,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gajibo</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3625,18 +4197,18 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>non_idp_NG008008_13</t>
+          <t>non_idp_NG008024_9</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3655,12 +4227,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gawa</t>
+          <t>Sugundure</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3670,7 +4242,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>non_idp_NG008008_14</t>
+          <t>non_idp_NG008024_supp11</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -3700,12 +4272,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Afuye</t>
+          <t>Ngurno</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3715,7 +4287,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>non_idp_NG008008_15</t>
+          <t>non_idp_NG008024_supp12</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -3745,12 +4317,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Gawa</t>
+          <t>Yele</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3760,7 +4332,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>non_idp_NG008008_16</t>
+          <t>non_idp_NG008024_supp14</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -3790,12 +4362,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Muliye</t>
+          <t>Ngurno</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3805,7 +4377,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>non_idp_NG008008_17</t>
+          <t>non_idp_NG008024_supp15</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -3835,12 +4407,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mudu Kaza</t>
+          <t>Kumalia</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3850,7 +4422,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>non_idp_NG008008_2</t>
+          <t>non_idp_NG008024_supp17</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -3880,12 +4452,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mudu Kaza</t>
+          <t>Kekeno</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3895,7 +4467,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>non_idp_NG008008_3</t>
+          <t>non_idp_NG008024_supp19</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -3925,12 +4497,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Gawa</t>
+          <t>Kumalia</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3940,7 +4512,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>non_idp_NG008008_4</t>
+          <t>non_idp_NG008024_supp22</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -3970,12 +4542,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3985,7 +4557,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>non_idp_NG008008_5</t>
+          <t>non_idp_NG008024_supp26</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -4015,12 +4587,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4030,18 +4602,18 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>non_idp_NG008008_6</t>
+          <t>non_idp_NG008024_supp27</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4060,12 +4632,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4075,7 +4647,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>non_idp_NG008008_9</t>
+          <t>non_idp_NG008024_supp28</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -4105,12 +4677,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Dikwa</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Mudu Kaza</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4120,7 +4692,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>non_idp_NG008008_supp1</t>
+          <t>non_idp_NG008024_supp3</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -4155,32 +4727,28 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Monguno</t>
+          <t>Mandala</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>idp_NG008024_1</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>In-camp</t>
-        </is>
-      </c>
+          <t>non_idp_NG008024_supp4</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4191,661 +4759,23 @@
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Borno</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Monguno</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Monguno</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>IDP</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>idp_NG008024_10</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>In-camp</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" s="10" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Borno</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Monguno</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Monguno</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>IDP</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>idp_NG008024_5</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>In-camp</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" s="10" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Borno</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Monguno</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Mintar</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>non_idp_NG008024_1</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" s="10" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Borno</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Monguno</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Monguno</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>non_idp_NG008024_11</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" s="10" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Borno</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Monguno</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Mofio</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>non_idp_NG008024_17</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" s="10" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Borno</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Monguno</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Kekeno</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>non_idp_NG008024_2</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" s="10" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Borno</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Monguno</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Mofio</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>non_idp_NG008024_3</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" s="10" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Borno</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Monguno</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Wulo</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>non_idp_NG008024_4</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" s="10" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Borno</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Monguno</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Wulo</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>non_idp_NG008024_5</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" s="10" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Borno</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Monguno</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Mintar</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>non_idp_NG008024_6</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" s="10" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Borno</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Monguno</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Monguno</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>non_idp_NG008024_7</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" s="10" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Borno</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Monguno</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Monguno</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>non_idp_NG008024_9</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" s="10" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Borno</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Monguno</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Sure</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>non_idp_NG008024_supp1</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" s="10" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Borno</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Monguno</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Wulo</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>non_idp_NG008024_supp2</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" s="10" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-    </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="I2:I59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M59" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="M2:M45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-08-28</formula2>
+      <formula2>2026-09-20</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5111,13 +5041,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DCDD53C-F637-49B9-B149-FC1486876560}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B37A53A1-2ED1-4757-9ECE-193FAE9D40DB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{849189E5-6519-4EAA-BA4D-C920FAF68E0C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94542F8A-E59E-4E21-A433-5B8C6A606A88}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAF719FA-8FC8-46B5-973D-78C847B3892C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F59F719C-A38E-4A7E-8442-229F208305AD}"/>
 </file>
--- a/resampling/input/accessibility_reports_generated/Street Child of Nigeria_accessibility_report.xlsx
+++ b/resampling/input/accessibility_reports_generated/Street Child of Nigeria_accessibility_report.xlsx
@@ -210,24 +210,25 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:O45" headerRowCount="1">
-  <autoFilter ref="A1:O45"/>
-  <tableColumns count="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ClusterAccessibility" displayName="ClusterAccessibility" ref="A1:P44" headerRowCount="1">
+  <autoFilter ref="A1:P44"/>
+  <tableColumns count="16">
     <tableColumn id="1" name="State"/>
     <tableColumn id="2" name="LGA"/>
     <tableColumn id="3" name="Ward (GRID3)"/>
     <tableColumn id="4" name="Pop Type"/>
     <tableColumn id="5" name="Cluster ID"/>
-    <tableColumn id="6" name="IDP Category"/>
-    <tableColumn id="7" name="Target HHs (primary)"/>
-    <tableColumn id="8" name="Reserve HHs"/>
-    <tableColumn id="9" name="Accessible (Y/N)"/>
-    <tableColumn id="10" name="Reason category"/>
-    <tableColumn id="11" name="Reason notes"/>
-    <tableColumn id="12" name="% of target achieved so far"/>
-    <tableColumn id="13" name="Date reported"/>
-    <tableColumn id="14" name="Reported by (Partner / IMPACT-default)"/>
-    <tableColumn id="15" name="Source channel"/>
+    <tableColumn id="6" name="Status"/>
+    <tableColumn id="7" name="IDP Category"/>
+    <tableColumn id="8" name="Target HHs (primary)"/>
+    <tableColumn id="9" name="Reserve HHs"/>
+    <tableColumn id="10" name="Accessible (Y/N)"/>
+    <tableColumn id="11" name="Reason category"/>
+    <tableColumn id="12" name="Reason notes"/>
+    <tableColumn id="13" name="% of target achieved so far"/>
+    <tableColumn id="14" name="Date reported"/>
+    <tableColumn id="15" name="Reported by (Partner / IMPACT-default)"/>
+    <tableColumn id="16" name="Source channel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -522,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -553,7 +554,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Assigned to you: 38 wards, 44 clusters</t>
+          <t>Assigned to you: 38 wards, 43 clusters</t>
         </is>
       </c>
     </row>
@@ -580,7 +581,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>A row with a very small Total target HHs figure (1-2) usually means a border case - GRID3 and OCHA/COD boundaries don't always agree exactly, so a small part of one of your clusters can fall just inside a ward you don't otherwise work in. This is expected, not an error - please still report on it like any other row if it's genuinely inaccessible. If a row also shows 'Yes' under 'Ward spans multiple LGAs', see that row's Note for what part of the ward is actually yours to report on.</t>
+          <t>If you've reported on a row before, your last answer is already shown here (Accessible/Reason/Date reported etc.) rather than a blank cell - please review it and only change it if something has actually changed since you last told us, don't assume a filled-in row is a mistake. On the 'Cluster Accessibility' sheet, a cluster you previously flagged that's since been removed from your assigned list entirely still appears, marked 'No longer in frame' in the Status column - kept so your earlier report isn't lost, but it's no longer something we need action on.</t>
         </is>
       </c>
     </row>
@@ -590,7 +591,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>For each ward, set Accessible (Y/N). Leave a ward's row otherwise blank if there's no issue there.</t>
+          <t>A row with a very small Total target HHs figure (1-2) usually means a border case - GRID3 and OCHA/COD boundaries don't always agree exactly, so a small part of one of your clusters can fall just inside a ward you don't otherwise work in. This is expected, not an error - please still report on it like any other row if it's genuinely inaccessible. If a row also shows 'Yes' under 'Ward spans multiple LGAs', see that row's Note for what part of the ward is actually yours to report on.</t>
         </is>
       </c>
     </row>
@@ -600,7 +601,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>For any ward marked 'No', pick the closest-fitting Reason category from the dropdown (use 'Other' plus a note if none fit), and add specific Reason notes - e.g. 'active clashes reported near [location] in the past week' is far more useful to us than just 'insecure'.</t>
+          <t>For each ward, set Accessible (Y/N). Leave a ward's row otherwise blank if there's no issue there.</t>
         </is>
       </c>
     </row>
@@ -610,7 +611,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>If you know it, fill in roughly what % of the target sample you were able to achieve in that ward before stopping - even a rough estimate helps, and please don't leave this blank if the true answer is 0%.</t>
+          <t>For any ward marked 'No', pick the closest-fitting Reason category from the dropdown (use 'Other' plus a note if none fit), and add specific Reason notes - e.g. 'active clashes reported near [location] in the past week' is far more useful to us than just 'insecure'.</t>
         </is>
       </c>
     </row>
@@ -620,7 +621,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>The last two columns ('Reported by' and 'Source channel') are for our own internal record-keeping - please leave them blank unless we've asked you to fill in a specific row on our behalf (e.g. transcribing a WhatsApp/verbal report into this sheet).</t>
+          <t>If you know it, fill in roughly what % of the target sample you were able to achieve in that ward before stopping - even a rough estimate helps, and please don't leave this blank if the true answer is 0%.</t>
         </is>
       </c>
     </row>
@@ -630,7 +631,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
+          <t>The last two columns ('Reported by' and 'Source channel') are for our own internal record-keeping - please leave them blank unless we've asked you to fill in a specific row on our behalf (e.g. transcribing a WhatsApp/verbal report into this sheet).</t>
         </is>
       </c>
     </row>
@@ -640,58 +641,68 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Date reported must be an actual date, not typed text - click the cell and use Excel's date picker, or type it as e.g. 27-Aug-2026. The cell will reject anything that isn't a real date, or a date before 01 Jul 2026/after today.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="90" customHeight="1">
+          <t>Only use the 'Cluster Accessibility' sheet (second tab) for a problem specific to ONE site/HH within an otherwise-fine ward - and only once you've already worked through that cluster's reserve/replacement households and they weren't enough to cover it. Don't use this sheet before exhausting your reserve list for that cluster, and don't use it as a second way to report the same ward-wide issue already captured on the first sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Date reported must be an actual date, not typed text - click the cell and use Excel's date picker, or type it as e.g. 27-Aug-2026. The cell will reject anything that isn't a real date, or a date before 01 Jul 2026/after today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>IMPORTANT: please review your ENTIRE coverage area in one pass before sending this back to us, rather than reporting a few wards now and more later - this significantly cuts down the back-and-forth rounds we need with you. If genuinely new information comes in afterwards, send an updated copy of the FULL sheet (not just the changed rows) with a new Date reported - we track changes over time by date, so we don't need you to tell us what changed, just the current full picture.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Which sheet do I use?</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Use for</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Ward Accessibility</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
+          <t>Ward Accessibility</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Your main report. Use for any access problem affecting a ward generally - insecurity, flooding/terrain, population displacement, denied access, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
           <t>Cluster Accessibility</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Secondary/detail only. Use ONLY for a problem specific to one site/HH, not the surrounding ward, and only after that cluster's reserve/replacement households were already used and weren't enough.</t>
         </is>
@@ -849,13 +860,13 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I2" t="n">
         <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -878,14 +889,10 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Madagali</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Madagali</t>
-        </is>
-      </c>
+          <t>Bebel</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>No</t>
@@ -894,13 +901,13 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -923,37 +930,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Garta</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Pallam</t>
-        </is>
-      </c>
+          <t>Bita Izge</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Michika</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -976,17 +971,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bebel</t>
+          <t>Duhu</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
@@ -1017,17 +1020,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bita Izge</t>
+          <t>Garta</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
@@ -1058,25 +1069,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Duhu</t>
+          <t>Hambagda Limankara Jaje</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Michika</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>0</v>
       </c>
@@ -1107,7 +1110,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hambagda Limankara Jaje</t>
+          <t>Hyambula</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1148,17 +1151,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hyambula</t>
+          <t>Kirchinga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Michika</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
@@ -1189,25 +1200,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kirchinga</t>
+          <t>Madagali</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Michika</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>0</v>
       </c>
@@ -1562,7 +1565,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Kumalia</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1581,13 +1584,13 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J18" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -1663,14 +1666,10 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ngurno</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Ngurno</t>
-        </is>
-      </c>
+          <t>Alarge</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1678,7 +1677,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kukawa</t>
+          <t>Guzamala; Nganzai</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1687,13 +1686,13 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -1716,37 +1715,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kumalia</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Monguno</t>
-        </is>
-      </c>
+          <t>Badairi</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Guzamala</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1769,29 +1756,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mandala</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Mandala</t>
-        </is>
-      </c>
+          <t>Damakulli</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mafa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -1814,14 +1805,10 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sugundure</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Zulum</t>
-        </is>
-      </c>
+          <t>Kabulawa</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1829,7 +1816,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nganzai</t>
+          <t>Mafa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1838,13 +1825,13 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -1867,14 +1854,10 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yele</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Yele</t>
-        </is>
-      </c>
+          <t>Kaguram</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>No</t>
@@ -1883,13 +1866,13 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -1912,14 +1895,10 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yoyo</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Kumalia</t>
-        </is>
-      </c>
+          <t>Kingarwa</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1927,7 +1906,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guzamala; Kukawa</t>
+          <t>Guzamala</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1936,13 +1915,13 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -1965,25 +1944,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alarge</t>
+          <t>Kirenowa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Guzamala; Nganzai</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>0</v>
       </c>
@@ -2014,17 +1985,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Badairi</t>
+          <t>Kumalia</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Guzamala</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
@@ -2055,7 +2034,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Damakulli</t>
+          <t>Maiwa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2066,7 +2045,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mafa</t>
+          <t>Mafa; Nganzai</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2104,25 +2083,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kabulawa</t>
+          <t>Mandala</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Mafa</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>0</v>
       </c>
@@ -2153,17 +2124,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kaguram</t>
+          <t>Masu</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Jere; Mafa; Nganzai</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
@@ -2194,7 +2173,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kingarwa</t>
+          <t>Mintar</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2205,7 +2184,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Guzamala</t>
+          <t>Kukawa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2243,17 +2222,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kirenowa</t>
+          <t>Mofio</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mafa; Nganzai</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
+        </is>
+      </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
@@ -2284,7 +2271,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Maiwa</t>
+          <t>Ngurno</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2295,7 +2282,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mafa; Nganzai</t>
+          <t>Kukawa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2333,7 +2320,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Masu</t>
+          <t>Sugundure</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -2344,7 +2331,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Jere; Mafa; Nganzai</t>
+          <t>Nganzai</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2382,25 +2369,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mintar</t>
+          <t>Sure</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Kukawa</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>This ward's GRID3 polygon spans more than one LGA - you only need to report on the part of the ward that falls within your own LGA coverage. See the 'Other LGA(s) sharing this ward' column for where the rest of it sits.</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>0</v>
       </c>
@@ -2431,7 +2410,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mofio</t>
+          <t>Wulo</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -2442,7 +2421,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mafa; Nganzai</t>
+          <t>Guzamala</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2480,7 +2459,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sure</t>
+          <t>Yele</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -2521,7 +2500,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wulo</t>
+          <t>Yoyo</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -2532,7 +2511,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guzamala</t>
+          <t>Guzamala; Kukawa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2614,7 +2593,7 @@
     </dataValidation>
     <dataValidation sqref="O2:O39" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-09-20</formula2>
+      <formula2>2026-09-21</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2630,7 +2609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2638,16 +2617,17 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2678,50 +2658,55 @@
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
           <t>IDP Category</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Target HHs (primary)</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Reserve HHs</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Accessible (Y/N)</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>Reason category</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>Reason notes</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>% of target achieved so far</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>Date reported</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>Reported by (Partner / IMPACT-default)</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>Source channel</t>
         </is>
@@ -2755,26 +2740,31 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2789,7 +2779,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Madagali</t>
+          <t>Gulak</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2799,31 +2789,36 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>idp_NG002010_15</t>
+          <t>idp_NG002010_6</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="10" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2838,7 +2833,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Madagali</t>
+          <t>Gulak</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2848,31 +2843,36 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>idp_NG002010_16</t>
+          <t>idp_NG002010_supp1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="10" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Madagali</t>
+          <t>Gulak</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2897,31 +2897,36 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>idp_NG002010_17</t>
+          <t>idp_NG002010_supp2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="10" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2946,31 +2951,36 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>idp_NG002010_6</t>
+          <t>idp_NG002010_supp3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>In-host</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2990,36 +3000,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>idp_NG002010_supp1</t>
+          <t>non_idp_NG002010_1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="10" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3039,36 +3050,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>idp_NG002010_supp2</t>
+          <t>non_idp_NG002010_3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="10" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3088,36 +3100,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>idp_NG002010_supp3</t>
+          <t>non_idp_NG002010_4</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="10" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3132,41 +3145,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Madagali</t>
+          <t>Gulak</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>idp_NG002010_supp4</t>
+          <t>non_idp_NG002010_7</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3181,41 +3195,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Madagali</t>
+          <t>Gulak</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>IDP</t>
+          <t>Non-IDP</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>idp_NG002010_supp5</t>
+          <t>non_idp_NG002010_supp1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>In-host</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3240,27 +3255,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_1</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG002010_supp11</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="10" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3275,7 +3295,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Madagali</t>
+          <t>Gulak</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3285,27 +3305,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_15</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>non_idp_NG002010_supp12</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="10" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3330,27 +3355,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_3</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG002010_supp13</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3375,27 +3405,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_4</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>non_idp_NG002010_supp14</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3420,27 +3455,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_7</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG002010_supp16</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="10" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3465,27 +3505,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_supp1</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG002010_supp2</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" s="10" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3500,7 +3545,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Madagali</t>
+          <t>Gulak</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3510,27 +3555,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_supp10</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG002010_supp4</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="10" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3555,193 +3605,229 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_supp11</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG002010_supp9</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="10" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Adamawa</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Madagali</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gulak</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_supp12</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>idp_NG008024_1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" s="10" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Adamawa</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Madagali</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gulak</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_supp13</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>idp_NG008024_10</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="10" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Adamawa</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Madagali</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Gulak</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_supp2</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>idp_NG008024_5</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="10" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Adamawa</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Madagali</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Garta</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_supp3</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>idp_NG008024_supp1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3749,44 +3835,53 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="10" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Adamawa</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Madagali</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gulak</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_supp4</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>idp_NG008024_supp10</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3794,44 +3889,53 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" s="10" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Adamawa</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Madagali</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Madagali</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_supp8</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>idp_NG008024_supp11</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3839,44 +3943,53 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" s="10" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Adamawa</t>
+          <t>Borno</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Madagali</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Gulak</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>non_idp_NG002010_supp9</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>idp_NG008024_supp2</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3884,13 +3997,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" s="10" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3915,31 +4033,36 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>idp_NG008024_1</t>
+          <t>idp_NG008024_supp3</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>In-camp</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" s="10" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3964,31 +4087,36 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>idp_NG008024_10</t>
+          <t>idp_NG008024_supp4</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>In-camp</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="10" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4013,31 +4141,36 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>idp_NG008024_5</t>
+          <t>idp_NG008024_supp5</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>In-camp</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" s="10" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4057,32 +4190,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>non_idp_NG008024_11</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>idp_NG008024_supp6</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="10" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4097,23 +4239,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kekeno</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>non_idp_NG008024_2</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>idp_NG008024_supp7</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>In-camp</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4121,13 +4267,18 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" s="10" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4147,32 +4298,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>non_idp_NG008024_7</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>idp_NG008024_supp8</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" s="10" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4192,32 +4352,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Non-IDP</t>
+          <t>IDP</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>non_idp_NG008024_9</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>idp_NG008024_supp9</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>In-host</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" s="10" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4232,7 +4401,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sugundure</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4242,27 +4411,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>non_idp_NG008024_supp11</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008024_11</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" s="10" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4277,7 +4451,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ngurno</t>
+          <t>Kekeno</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4287,27 +4461,48 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>non_idp_NG008024_supp12</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008024_2</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>N/A - fully accessible</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" s="10" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Partner's own template</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4322,7 +4517,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Yele</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4332,27 +4527,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>non_idp_NG008024_supp14</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008024_7</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" s="10" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4367,7 +4567,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ngurno</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4377,27 +4577,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>non_idp_NG008024_supp15</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008024_9</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" s="10" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4412,7 +4617,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kumalia</t>
+          <t>Kekeno</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4422,27 +4627,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>non_idp_NG008024_supp17</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008024_supp19</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" s="10" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4457,7 +4667,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kekeno</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4467,27 +4677,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>non_idp_NG008024_supp19</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008024_supp26</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" s="10" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4502,7 +4717,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kumalia</t>
+          <t>Monguno</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4512,27 +4727,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>non_idp_NG008024_supp22</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008024_supp27</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" s="10" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4557,27 +4777,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>non_idp_NG008024_supp26</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008024_supp28</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" s="10" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4602,27 +4827,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>non_idp_NG008024_supp27</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008024_supp29</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" s="10" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4647,27 +4877,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>non_idp_NG008024_supp28</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008024_supp3</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" s="10" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4692,90 +4927,50 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>non_idp_NG008024_supp3</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>non_idp_NG008024_supp30</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" s="10" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Borno</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Monguno</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Mandala</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Non-IDP</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>non_idp_NG008024_supp4</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" s="10" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="I2:I45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N/A - fully accessible,Insecurity / conflict,Physical access (terrain, flooding, roads),Population absent / relocated,Building-footprint issue (no eligible structures),Access denied by authorities / community,Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner,IMPACT (default - accessible until reported otherwise)"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Partner's own template,Email,WhatsApp/verbal (coordinator-transcribed),Point-level file annotation,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
+    <dataValidation sqref="N2:N44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid date" error="Enter an actual date between 01 Jul 2026 and today - click the cell and use the date picker, or type e.g. 27-Aug-2026. Free text and out-of-range dates (including future dates) are rejected here so they don't need to be caught and excluded later." type="date" operator="between">
       <formula1>2026-07-01</formula1>
-      <formula2>2026-09-20</formula2>
+      <formula2>2026-09-21</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5041,13 +5236,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B37A53A1-2ED1-4757-9ECE-193FAE9D40DB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CECF184-83F7-4CE1-BD65-DCBEB956BC39}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94542F8A-E59E-4E21-A433-5B8C6A606A88}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E33957B-6704-428F-9364-EB5A5C01656F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F59F719C-A38E-4A7E-8442-229F208305AD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE3442A1-F34C-4970-9FA8-B06F6DDCA518}"/>
 </file>